--- a/testData/register_user.xlsx
+++ b/testData/register_user.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SeleniumLearning\LambdatestPlayground\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E4ECF6-9DA8-4CCA-AA39-B17BA9DE17CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52362E77-C92C-4C81-B601-7F0D6F202757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A74BF28C-13B3-448C-A368-528222B83AEA}"/>
   </bookViews>
@@ -144,7 +144,7 @@
     <t>AhsanHafiz</t>
   </si>
   <si>
-    <t>q01afiz@gmail.com</t>
+    <t>asdfg12345@gmail.com</t>
   </si>
   <si>
     <t>Test Passed</t>
